--- a/evac_by_zip/evac_by_zip_2026-09-01.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-09-01.xlsx
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 196 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 198 addresses (across 1 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C5" s="8" t="n">
         <v>3</v>
@@ -683,7 +683,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="7" t="n">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>341</v>
@@ -1157,7 +1157,7 @@
         <v>44</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>1456</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="20">
@@ -1170,13 +1170,13 @@
         <v>158</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D20" s="16" t="n">
         <v>28</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21">
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="B21" s="18" t="n">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D21" s="18" t="n">
         <v>72</v>
@@ -1213,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B26" s="24" t="inlineStr">
         <is>
-          <t>US-OR-GRA-GRN-043-K</t>
+          <t>US-OR-GRA-GRN-043-L</t>
         </is>
       </c>
       <c r="C26" s="24" t="inlineStr">
@@ -2285,73 +2285,73 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>97877</t>
-        </is>
-      </c>
-      <c r="B32" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-GRA-GRN-043-L</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>Baker, Grant</t>
-        </is>
-      </c>
-      <c r="E32" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F32" s="25" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>2</v>
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>97827</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140618N</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Umatilla, Union</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="21" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-140618N</t>
-        </is>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624S</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="n">
-        <v>29</v>
+      <c r="E33" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F33" s="23" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G33" s="23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="B34" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624S</t>
+          <t>US-OR-UMA-UMC-1406024A</t>
         </is>
       </c>
       <c r="C34" s="24" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F34" s="23" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G34" s="23" t="n">
@@ -2390,38 +2390,38 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>97827</t>
         </is>
       </c>
-      <c r="B35" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406024A</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D35" s="24" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-140624N-B</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
         <is>
           <t>Umatilla, Union</t>
         </is>
       </c>
-      <c r="E35" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F35" s="23" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G35" s="23" t="n">
-        <v>1</v>
+      <c r="E35" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F35" s="25" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="B36" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-140624N-B</t>
+          <t>US-OR-UNI-UCO-1497</t>
         </is>
       </c>
       <c r="C36" s="26" t="inlineStr">
@@ -2452,11 +2452,11 @@
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="G36" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="B37" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1497</t>
+          <t>US-OR-UNI-UCO-1505</t>
         </is>
       </c>
       <c r="C37" s="26" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="F37" s="25" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G37" s="25" t="n">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="B38" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1505</t>
+          <t>US-OR-UNI-UCO-1513</t>
         </is>
       </c>
       <c r="C38" s="26" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G38" s="25" t="n">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="B39" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1513</t>
+          <t>US-OR-UMA-UMC-1406030-A</t>
         </is>
       </c>
       <c r="C39" s="26" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>1%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G39" s="25" t="n">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B40" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406030-A</t>
+          <t>US-OR-UNI-UCO-1495</t>
         </is>
       </c>
       <c r="C40" s="26" t="inlineStr">
@@ -2600,37 +2600,37 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>97827</t>
-        </is>
-      </c>
-      <c r="B41" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1495</t>
-        </is>
-      </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D41" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla, Union</t>
-        </is>
-      </c>
-      <c r="E41" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F41" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G41" s="25" t="n">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>97814</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1119-B</t>
+        </is>
+      </c>
+      <c r="C41" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1119-B</t>
+          <t>US-OR-BAK-BAB-1247</t>
         </is>
       </c>
       <c r="C42" s="22" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="F42" s="21" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G42" s="21" t="n">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1247</t>
+          <t>US-OR-BAK-BAB-1246</t>
         </is>
       </c>
       <c r="C43" s="22" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="F43" s="21" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G43" s="21" t="n">
@@ -2705,73 +2705,73 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="21" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>97814</t>
         </is>
       </c>
-      <c r="B44" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1246</t>
-        </is>
-      </c>
-      <c r="C44" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D44" s="22" t="inlineStr">
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-SMT-636</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E44" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F44" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G44" s="21" t="n">
+      <c r="E44" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F44" s="23" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
+      <c r="G44" s="23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>97814</t>
         </is>
       </c>
-      <c r="B45" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-SMT-636</t>
-        </is>
-      </c>
-      <c r="C45" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D45" s="24" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1252</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E45" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F45" s="23" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>1</v>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F45" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B46" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1252</t>
+          <t>US-OR-BAK-SMT-610</t>
         </is>
       </c>
       <c r="C46" s="26" t="inlineStr">
@@ -2802,11 +2802,11 @@
       </c>
       <c r="F46" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G46" s="25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="B47" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-610</t>
+          <t>US-OR-BAK-SMT-600</t>
         </is>
       </c>
       <c r="C47" s="26" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="B48" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-SMT-600</t>
+          <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
       <c r="C48" s="26" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G48" s="25" t="n">
@@ -2880,73 +2880,73 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="25" t="inlineStr">
-        <is>
-          <t>97814</t>
-        </is>
-      </c>
-      <c r="B49" s="26" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>US-OR-BAK-BAB-1119-B</t>
+        </is>
+      </c>
+      <c r="C49" s="22" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D49" s="22" t="inlineStr">
+        <is>
+          <t>Baker</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G49" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="25" t="inlineStr">
+        <is>
+          <t>97833</t>
+        </is>
+      </c>
+      <c r="B50" s="26" t="inlineStr">
         <is>
           <t>US-OR-BAK-BAB-1242</t>
         </is>
       </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D49" s="26" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
         <is>
           <t>Baker</t>
         </is>
       </c>
-      <c r="E49" s="25" t="inlineStr">
+      <c r="E50" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F49" s="25" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G49" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="21" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1119-B</t>
-        </is>
-      </c>
-      <c r="C50" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D50" s="22" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E50" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F50" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G50" s="21" t="n">
-        <v>1</v>
+      <c r="F50" s="25" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+      <c r="G50" s="25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="B51" s="26" t="inlineStr">
         <is>
-          <t>US-OR-BAK-BAB-1242</t>
+          <t>US-OR-BAK-BAB-1252</t>
         </is>
       </c>
       <c r="C51" s="26" t="inlineStr">
@@ -2977,67 +2977,67 @@
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G51" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="25" t="inlineStr">
-        <is>
-          <t>97833</t>
-        </is>
-      </c>
-      <c r="B52" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-BAK-BAB-1252</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="inlineStr">
-        <is>
-          <t>Baker</t>
-        </is>
-      </c>
-      <c r="E52" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F52" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G52" s="25" t="n">
-        <v>1</v>
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>97021</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>NF 27</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Grasshopper</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Wasco</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F52" s="21" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G52" s="21" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="21" t="inlineStr">
         <is>
-          <t>97021</t>
+          <t>97023</t>
         </is>
       </c>
       <c r="B53" s="22" t="inlineStr">
         <is>
-          <t>NF 27</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C53" s="22" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D53" s="22" t="inlineStr">
         <is>
-          <t>Wasco</t>
+          <t>Clackamas</t>
         </is>
       </c>
       <c r="E53" s="21" t="inlineStr">
@@ -3047,32 +3047,32 @@
       </c>
       <c r="F53" s="21" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="G53" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="21" t="inlineStr">
         <is>
-          <t>97023</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>NF 27</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="D54" s="22" t="inlineStr">
         <is>
-          <t>Clackamas</t>
+          <t>Wasco</t>
         </is>
       </c>
       <c r="E54" s="21" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="F54" s="21" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="G54" s="21" t="n">
@@ -3092,71 +3092,71 @@
     <row r="55">
       <c r="A55" s="21" t="inlineStr">
         <is>
-          <t>97063</t>
+          <t>97358</t>
         </is>
       </c>
       <c r="B55" s="22" t="inlineStr">
         <is>
-          <t>NF 27</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C55" s="22" t="inlineStr">
         <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="inlineStr">
+        <is>
+          <t>Clackamas</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="inlineStr">
+        <is>
+          <t>Level 3 — GO NOW</t>
+        </is>
+      </c>
+      <c r="F55" s="21" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G55" s="21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>97041</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Elk Mountain</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D55" s="22" t="inlineStr">
-        <is>
-          <t>Wasco</t>
-        </is>
-      </c>
-      <c r="E55" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F55" s="21" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="G55" s="21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="inlineStr">
-        <is>
-          <t>97358</t>
-        </is>
-      </c>
-      <c r="B56" s="22" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="C56" s="22" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D56" s="22" t="inlineStr">
-        <is>
-          <t>Clackamas</t>
-        </is>
-      </c>
-      <c r="E56" s="21" t="inlineStr">
-        <is>
-          <t>Level 3 — GO NOW</t>
-        </is>
-      </c>
-      <c r="F56" s="21" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G56" s="21" t="n">
-        <v>1</v>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>Hood River</t>
+        </is>
+      </c>
+      <c r="E56" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F56" s="23" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="G56" s="23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>Elk Mountain</t>
+          <t>Mill Creek Buttes</t>
         </is>
       </c>
       <c r="C57" s="24" t="inlineStr">
@@ -3187,46 +3187,46 @@
       </c>
       <c r="F57" s="23" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G57" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="23" t="inlineStr">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>97041</t>
         </is>
       </c>
-      <c r="B58" s="24" t="inlineStr">
-        <is>
-          <t>Mill Creek Buttes</t>
-        </is>
-      </c>
-      <c r="C58" s="24" t="inlineStr">
+      <c r="B58" s="26" t="inlineStr">
+        <is>
+          <t>Cooper Spur North</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D58" s="24" t="inlineStr">
+      <c r="D58" s="26" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E58" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F58" s="23" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
-      </c>
-      <c r="G58" s="23" t="n">
-        <v>2</v>
+      <c r="E58" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F58" s="25" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G58" s="25" t="n">
+        <v>158</v>
       </c>
     </row>
     <row r="59">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="B59" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur North</t>
+          <t>Cooper Spur South</t>
         </is>
       </c>
       <c r="C59" s="26" t="inlineStr">
@@ -3257,11 +3257,11 @@
       </c>
       <c r="F59" s="25" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G59" s="25" t="n">
-        <v>158</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="B60" s="26" t="inlineStr">
         <is>
-          <t>Cooper Spur South</t>
+          <t>Gibson Prairie</t>
         </is>
       </c>
       <c r="C60" s="26" t="inlineStr">
@@ -3292,11 +3292,11 @@
       </c>
       <c r="F60" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="G60" s="25" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="B61" s="26" t="inlineStr">
         <is>
-          <t>Gibson Prairie</t>
+          <t>White River</t>
         </is>
       </c>
       <c r="C61" s="26" t="inlineStr">
@@ -3327,46 +3327,46 @@
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="G61" s="25" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="25" t="inlineStr">
-        <is>
-          <t>97041</t>
-        </is>
-      </c>
-      <c r="B62" s="26" t="inlineStr">
-        <is>
-          <t>White River</t>
-        </is>
-      </c>
-      <c r="C62" s="26" t="inlineStr">
-        <is>
-          <t>Grasshopper</t>
-        </is>
-      </c>
-      <c r="D62" s="26" t="inlineStr">
-        <is>
-          <t>Hood River</t>
-        </is>
-      </c>
-      <c r="E62" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F62" s="25" t="inlineStr">
-        <is>
-          <t>42%</t>
-        </is>
-      </c>
-      <c r="G62" s="25" t="n">
-        <v>1</v>
+      <c r="A62" s="23" t="inlineStr">
+        <is>
+          <t>97810</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-1406017-A</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E62" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F62" s="23" t="inlineStr">
+        <is>
+          <t>89%</t>
+        </is>
+      </c>
+      <c r="G62" s="23" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="63">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="B63" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406017-A</t>
+          <t>US-OR-UMA-UMC-1406053-C</t>
         </is>
       </c>
       <c r="C63" s="24" t="inlineStr">
@@ -3397,11 +3397,11 @@
       </c>
       <c r="F63" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G63" s="23" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B64" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406053-C</t>
+          <t>US-OR-UMA-UMC-1406015-E</t>
         </is>
       </c>
       <c r="C64" s="24" t="inlineStr">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="G64" s="23" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B65" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-E</t>
+          <t>US-OR-UMA-UMC-153</t>
         </is>
       </c>
       <c r="C65" s="24" t="inlineStr">
@@ -3467,11 +3467,11 @@
       </c>
       <c r="F65" s="23" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G65" s="23" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B66" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-153</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C66" s="24" t="inlineStr">
@@ -3502,11 +3502,11 @@
       </c>
       <c r="F66" s="23" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="G66" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="B67" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-UMA-UMC-1406015G</t>
         </is>
       </c>
       <c r="C67" s="24" t="inlineStr">
@@ -3537,11 +3537,11 @@
       </c>
       <c r="F67" s="23" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G67" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="B68" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015G</t>
+          <t>US-OR-UMA-UMC-1406015-C</t>
         </is>
       </c>
       <c r="C68" s="24" t="inlineStr">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="G68" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="B69" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406015-C</t>
+          <t>US-OR-UMA-UMC-1406053-B</t>
         </is>
       </c>
       <c r="C69" s="24" t="inlineStr">
@@ -3611,42 +3611,42 @@
         </is>
       </c>
       <c r="G69" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="23" t="inlineStr">
+      <c r="A70" s="25" t="inlineStr">
         <is>
           <t>97810</t>
         </is>
       </c>
-      <c r="B70" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406053-B</t>
-        </is>
-      </c>
-      <c r="C70" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D70" s="24" t="inlineStr">
+      <c r="B70" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-215-C</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D70" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E70" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F70" s="23" t="inlineStr">
+      <c r="E70" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F70" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G70" s="23" t="n">
-        <v>1</v>
+      <c r="G70" s="25" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="71">
@@ -3657,7 +3657,7 @@
       </c>
       <c r="B71" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-C</t>
+          <t>US-OR-UMA-UMC-215-E</t>
         </is>
       </c>
       <c r="C71" s="26" t="inlineStr">
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="G71" s="25" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B72" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-E</t>
+          <t>US-OR-UMA-UMC-215-D</t>
         </is>
       </c>
       <c r="C72" s="26" t="inlineStr">
@@ -3716,7 +3716,7 @@
         </is>
       </c>
       <c r="G72" s="25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -3727,7 +3727,7 @@
       </c>
       <c r="B73" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-D</t>
+          <t>US-OR-UMA-UMC-215-F</t>
         </is>
       </c>
       <c r="C73" s="26" t="inlineStr">
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="G73" s="25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="B74" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-215-F</t>
+          <t>US-OR-UMA-UMC-151-D</t>
         </is>
       </c>
       <c r="C74" s="26" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F74" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="G74" s="25" t="n">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="B75" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-151-D</t>
+          <t>US-OR-UMA-UMC-149-B</t>
         </is>
       </c>
       <c r="C75" s="26" t="inlineStr">
@@ -3817,11 +3817,11 @@
       </c>
       <c r="F75" s="25" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="G75" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="B76" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-149-B</t>
+          <t>US-OR-UMA-UMC-155-B</t>
         </is>
       </c>
       <c r="C76" s="26" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F76" s="25" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G76" s="25" t="n">
@@ -3860,38 +3860,38 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="25" t="inlineStr">
-        <is>
-          <t>97810</t>
-        </is>
-      </c>
-      <c r="B77" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-155-B</t>
-        </is>
-      </c>
-      <c r="C77" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D77" s="26" t="inlineStr">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>99362</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E77" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F77" s="25" t="inlineStr">
-        <is>
-          <t>9%</t>
-        </is>
-      </c>
-      <c r="G77" s="25" t="n">
-        <v>1</v>
+      <c r="E77" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F77" s="23" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G77" s="23" t="n">
+        <v>58</v>
       </c>
     </row>
     <row r="78">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B78" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-039</t>
+          <t>US-OR-UMA-UMC-1406043-C</t>
         </is>
       </c>
       <c r="C78" s="24" t="inlineStr">
@@ -3922,81 +3922,81 @@
       </c>
       <c r="F78" s="23" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G78" s="23" t="n">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="23" t="inlineStr">
+      <c r="A79" s="25" t="inlineStr">
         <is>
           <t>99362</t>
         </is>
       </c>
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-1406043-C</t>
-        </is>
-      </c>
-      <c r="C79" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D79" s="24" t="inlineStr">
+      <c r="B79" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D79" s="26" t="inlineStr">
         <is>
           <t>Umatilla</t>
         </is>
       </c>
-      <c r="E79" s="23" t="inlineStr">
+      <c r="E79" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F79" s="25" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="G79" s="25" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="23" t="inlineStr">
+        <is>
+          <t>97876</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1435</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>Union</t>
+        </is>
+      </c>
+      <c r="E80" s="23" t="inlineStr">
         <is>
           <t>Level 2 — GET SET</t>
         </is>
       </c>
-      <c r="F79" s="23" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G79" s="23" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="25" t="inlineStr">
-        <is>
-          <t>99362</t>
-        </is>
-      </c>
-      <c r="B80" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-032</t>
-        </is>
-      </c>
-      <c r="C80" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D80" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E80" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F80" s="25" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="G80" s="25" t="n">
-        <v>22</v>
+      <c r="F80" s="23" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G80" s="23" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1435</t>
+          <t>US-OR-UNI-UCO-1450</t>
         </is>
       </c>
       <c r="C81" s="24" t="inlineStr">
@@ -4027,46 +4027,46 @@
       </c>
       <c r="F81" s="23" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>36%</t>
         </is>
       </c>
       <c r="G81" s="23" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="23" t="inlineStr">
+      <c r="A82" s="25" t="inlineStr">
         <is>
           <t>97876</t>
         </is>
       </c>
-      <c r="B82" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1450</t>
-        </is>
-      </c>
-      <c r="C82" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D82" s="24" t="inlineStr">
+      <c r="B82" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UNI-UCO-1421</t>
+        </is>
+      </c>
+      <c r="C82" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D82" s="26" t="inlineStr">
         <is>
           <t>Union</t>
         </is>
       </c>
-      <c r="E82" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F82" s="23" t="inlineStr">
-        <is>
-          <t>36%</t>
-        </is>
-      </c>
-      <c r="G82" s="23" t="n">
-        <v>1</v>
+      <c r="E82" s="25" t="inlineStr">
+        <is>
+          <t>Level 1 — GET READY</t>
+        </is>
+      </c>
+      <c r="F82" s="25" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G82" s="25" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="83">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="B83" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1421</t>
+          <t>US-OR-UNI-UCO-1436</t>
         </is>
       </c>
       <c r="C83" s="26" t="inlineStr">
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="G83" s="25" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B84" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1436</t>
+          <t>US-OR-UNI-UCO-1437</t>
         </is>
       </c>
       <c r="C84" s="26" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B85" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UNI-UCO-1437</t>
+          <t>US-OR-UNI-UCO-1438</t>
         </is>
       </c>
       <c r="C85" s="26" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="F85" s="25" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G85" s="25" t="n">
@@ -4175,73 +4175,73 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="25" t="inlineStr">
-        <is>
-          <t>97876</t>
-        </is>
-      </c>
-      <c r="B86" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UNI-UCO-1438</t>
-        </is>
-      </c>
-      <c r="C86" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D86" s="26" t="inlineStr">
-        <is>
-          <t>Union</t>
-        </is>
-      </c>
-      <c r="E86" s="25" t="inlineStr">
+      <c r="A86" s="23" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-039</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E86" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F86" s="23" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="G86" s="23" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="25" t="inlineStr">
+        <is>
+          <t>97862</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>US-OR-UMA-UMC-032</t>
+        </is>
+      </c>
+      <c r="C87" s="26" t="inlineStr">
+        <is>
+          <t>No named fire</t>
+        </is>
+      </c>
+      <c r="D87" s="26" t="inlineStr">
+        <is>
+          <t>Umatilla</t>
+        </is>
+      </c>
+      <c r="E87" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F86" s="25" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G86" s="25" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="23" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B87" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-039</t>
-        </is>
-      </c>
-      <c r="C87" s="24" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D87" s="24" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E87" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F87" s="23" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="G87" s="23" t="n">
-        <v>7</v>
+      <c r="F87" s="25" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G87" s="25" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="88">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B88" s="26" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-032</t>
+          <t>US-OR-UMA-UMC-121-B</t>
         </is>
       </c>
       <c r="C88" s="26" t="inlineStr">
@@ -4272,45 +4272,45 @@
       </c>
       <c r="F88" s="25" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G88" s="25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="25" t="inlineStr">
-        <is>
-          <t>97862</t>
-        </is>
-      </c>
-      <c r="B89" s="26" t="inlineStr">
-        <is>
-          <t>US-OR-UMA-UMC-121-B</t>
-        </is>
-      </c>
-      <c r="C89" s="26" t="inlineStr">
-        <is>
-          <t>No named fire</t>
-        </is>
-      </c>
-      <c r="D89" s="26" t="inlineStr">
-        <is>
-          <t>Umatilla</t>
-        </is>
-      </c>
-      <c r="E89" s="25" t="inlineStr">
-        <is>
-          <t>Level 1 — GET READY</t>
-        </is>
-      </c>
-      <c r="F89" s="25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G89" s="25" t="n">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t>97639</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>US-OR-KLA-KLA-1381-D</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>Wrights Spring</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>Klamath</t>
+        </is>
+      </c>
+      <c r="E89" s="23" t="inlineStr">
+        <is>
+          <t>Level 2 — GET SET</t>
+        </is>
+      </c>
+      <c r="F89" s="23" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="G89" s="23" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="B90" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-D</t>
+          <t>US-OR-KLA-KLA-1381-B</t>
         </is>
       </c>
       <c r="C90" s="24" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="F90" s="23" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="G90" s="23" t="n">
@@ -4352,22 +4352,22 @@
     <row r="91">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t>97639</t>
+          <t>97859</t>
         </is>
       </c>
       <c r="B91" s="24" t="inlineStr">
         <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
+          <t>US-OR-UMA-UMC-1406007-B</t>
         </is>
       </c>
       <c r="C91" s="24" t="inlineStr">
         <is>
-          <t>Wrights Spring</t>
+          <t>No named fire</t>
         </is>
       </c>
       <c r="D91" s="24" t="inlineStr">
         <is>
-          <t>Klamath</t>
+          <t>Umatilla</t>
         </is>
       </c>
       <c r="E91" s="23" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="F91" s="23" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G91" s="23" t="n">
@@ -4387,22 +4387,22 @@
     <row r="92">
       <c r="A92" s="23" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="B92" s="24" t="inlineStr">
         <is>
-          <t>US-OR-UMA-UMC-1406007-B</t>
+          <t>US-OR-KLA-KLA-1381-B</t>
         </is>
       </c>
       <c r="C92" s="24" t="inlineStr">
         <is>
-          <t>No named fire</t>
+          <t>Wrights Spring</t>
         </is>
       </c>
       <c r="D92" s="24" t="inlineStr">
         <is>
-          <t>Umatilla</t>
+          <t>Klamath</t>
         </is>
       </c>
       <c r="E92" s="23" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F92" s="23" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G92" s="23" t="n">
@@ -4420,77 +4420,42 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="23" t="inlineStr">
-        <is>
-          <t>97624</t>
-        </is>
-      </c>
-      <c r="B93" s="24" t="inlineStr">
-        <is>
-          <t>US-OR-KLA-KLA-1381-B</t>
-        </is>
-      </c>
-      <c r="C93" s="24" t="inlineStr">
-        <is>
-          <t>Wrights Spring</t>
-        </is>
-      </c>
-      <c r="D93" s="24" t="inlineStr">
-        <is>
-          <t>Klamath</t>
-        </is>
-      </c>
-      <c r="E93" s="23" t="inlineStr">
-        <is>
-          <t>Level 2 — GET SET</t>
-        </is>
-      </c>
-      <c r="F93" s="23" t="inlineStr">
-        <is>
-          <t>16%</t>
-        </is>
-      </c>
-      <c r="G93" s="23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="25" t="inlineStr">
+      <c r="A93" s="25" t="inlineStr">
         <is>
           <t>97028</t>
         </is>
       </c>
-      <c r="B94" s="26" t="inlineStr">
+      <c r="B93" s="26" t="inlineStr">
         <is>
           <t>White River</t>
         </is>
       </c>
-      <c r="C94" s="26" t="inlineStr">
+      <c r="C93" s="26" t="inlineStr">
         <is>
           <t>Grasshopper</t>
         </is>
       </c>
-      <c r="D94" s="26" t="inlineStr">
+      <c r="D93" s="26" t="inlineStr">
         <is>
           <t>Hood River</t>
         </is>
       </c>
-      <c r="E94" s="25" t="inlineStr">
+      <c r="E93" s="25" t="inlineStr">
         <is>
           <t>Level 1 — GET READY</t>
         </is>
       </c>
-      <c r="F94" s="25" t="inlineStr">
+      <c r="F93" s="25" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="G94" s="25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" ht="60" customHeight="1">
-      <c r="A96" s="27" t="inlineStr">
+      <c r="G93" s="25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" ht="60" customHeight="1">
+      <c r="A95" s="27" t="inlineStr">
         <is>
           <t>Methodology: "% of Zone" = the share of this evac zone's total polygon area that falls within this ZIP's Census ZCTA boundary (area-weighted polygon intersection). "Est. Addresses" = the zone's total AddressesWithin (OEM) × that same area fraction — an area-weighted estimate, not a geocoded address count; assumes uniform address density across the zone polygon. Rows whose estimate rounds below 1 are shown as 1 rather than omitted, since the ZIP is still a real, known intersection for that zone. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA.</t>
         </is>
@@ -4498,7 +4463,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A96:G96"/>
+    <mergeCell ref="A95:G95"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
